--- a/public/templates/bam-medewerkers-template.xlsx
+++ b/public/templates/bam-medewerkers-template.xlsx
@@ -215,21 +215,6 @@
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
         <t>bv. +32 470 12 34 56</t>
-      </text>
-    </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
-      <text>
-        <t>Stad / kantoor</t>
-      </text>
-    </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
-      <text>
-        <t>bv. Marketing, Sales, HR</t>
-      </text>
-    </comment>
-    <comment ref="I4" authorId="0" shapeId="0">
-      <text>
-        <t>Optioneel</t>
       </text>
     </comment>
   </commentList>
@@ -525,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -553,6 +538,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -584,21 +570,6 @@
           <t>GSM</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Locatie tewerkstelling</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Afdeling</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>LinkedIn URL</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -629,21 +600,6 @@
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>+32 470 12 34 56</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Antwerpen</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/janapeeters</t>
         </is>
       </c>
     </row>
@@ -654,9 +610,6 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -665,9 +618,6 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -676,9 +626,6 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -687,9 +634,6 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -698,9 +642,6 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -709,9 +650,6 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -720,9 +658,6 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -731,9 +666,6 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -742,9 +674,6 @@
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -753,9 +682,6 @@
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -764,9 +690,6 @@
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -775,9 +698,6 @@
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -786,9 +706,6 @@
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -797,9 +714,6 @@
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -808,9 +722,6 @@
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -819,9 +730,6 @@
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -830,9 +738,6 @@
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -841,9 +746,6 @@
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -852,9 +754,6 @@
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -863,9 +762,6 @@
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -874,9 +770,6 @@
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
       <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -885,9 +778,6 @@
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -896,9 +786,6 @@
       <c r="D28" s="5" t="n"/>
       <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -907,9 +794,6 @@
       <c r="D29" s="5" t="n"/>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -918,9 +802,6 @@
       <c r="D30" s="5" t="n"/>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -929,9 +810,6 @@
       <c r="D31" s="5" t="n"/>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n"/>
@@ -940,9 +818,6 @@
       <c r="D32" s="5" t="n"/>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n"/>
@@ -951,9 +826,6 @@
       <c r="D33" s="5" t="n"/>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -962,9 +834,6 @@
       <c r="D34" s="5" t="n"/>
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -973,9 +842,6 @@
       <c r="D35" s="5" t="n"/>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n"/>
@@ -984,9 +850,6 @@
       <c r="D36" s="5" t="n"/>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n"/>
@@ -995,9 +858,6 @@
       <c r="D37" s="5" t="n"/>
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -1006,9 +866,6 @@
       <c r="D38" s="5" t="n"/>
       <c r="E38" s="5" t="n"/>
       <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -1017,9 +874,6 @@
       <c r="D39" s="5" t="n"/>
       <c r="E39" s="5" t="n"/>
       <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n"/>
@@ -1028,9 +882,6 @@
       <c r="D40" s="5" t="n"/>
       <c r="E40" s="5" t="n"/>
       <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n"/>
@@ -1039,9 +890,6 @@
       <c r="D41" s="5" t="n"/>
       <c r="E41" s="5" t="n"/>
       <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -1050,9 +898,6 @@
       <c r="D42" s="5" t="n"/>
       <c r="E42" s="5" t="n"/>
       <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -1061,9 +906,6 @@
       <c r="D43" s="5" t="n"/>
       <c r="E43" s="5" t="n"/>
       <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n"/>
@@ -1072,9 +914,6 @@
       <c r="D44" s="5" t="n"/>
       <c r="E44" s="5" t="n"/>
       <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n"/>
@@ -1083,9 +922,6 @@
       <c r="D45" s="5" t="n"/>
       <c r="E45" s="5" t="n"/>
       <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -1094,9 +930,6 @@
       <c r="D46" s="5" t="n"/>
       <c r="E46" s="5" t="n"/>
       <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -1105,9 +938,6 @@
       <c r="D47" s="5" t="n"/>
       <c r="E47" s="5" t="n"/>
       <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n"/>
@@ -1116,9 +946,6 @@
       <c r="D48" s="5" t="n"/>
       <c r="E48" s="5" t="n"/>
       <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n"/>
@@ -1127,9 +954,6 @@
       <c r="D49" s="5" t="n"/>
       <c r="E49" s="5" t="n"/>
       <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -1138,9 +962,6 @@
       <c r="D50" s="5" t="n"/>
       <c r="E50" s="5" t="n"/>
       <c r="F50" s="5" t="n"/>
-      <c r="G50" s="5" t="n"/>
-      <c r="H50" s="5" t="n"/>
-      <c r="I50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -1149,9 +970,6 @@
       <c r="D51" s="5" t="n"/>
       <c r="E51" s="5" t="n"/>
       <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n"/>
@@ -1160,9 +978,6 @@
       <c r="D52" s="5" t="n"/>
       <c r="E52" s="5" t="n"/>
       <c r="F52" s="5" t="n"/>
-      <c r="G52" s="5" t="n"/>
-      <c r="H52" s="5" t="n"/>
-      <c r="I52" s="5" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n"/>
@@ -1171,9 +986,6 @@
       <c r="D53" s="5" t="n"/>
       <c r="E53" s="5" t="n"/>
       <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -1182,9 +994,6 @@
       <c r="D54" s="5" t="n"/>
       <c r="E54" s="5" t="n"/>
       <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -1193,9 +1002,6 @@
       <c r="D55" s="5" t="n"/>
       <c r="E55" s="5" t="n"/>
       <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
